--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487660_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487660_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6011</v>
+        <v>4.8829</v>
       </c>
       <c r="E2" t="n">
-        <v>8.674799999999999</v>
+        <v>8.9566</v>
       </c>
       <c r="F2" t="n">
         <v>-4.0736</v>
@@ -610,10 +610,10 @@
         <v>0.7761</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6057</v>
+        <v>0.8875</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0011</v>
+        <v>0.2829</v>
       </c>
       <c r="U2" t="n">
         <v>0.6046</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9717</v>
+        <v>4.2724</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2647</v>
+        <v>4.9469</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2929</v>
+        <v>-0.6745</v>
       </c>
       <c r="G3" t="n">
         <v>3.0574</v>
@@ -688,13 +688,13 @@
         <v>0.7761</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7382</v>
+        <v>1.0389</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6539</v>
+        <v>0.0283</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3921</v>
+        <v>1.0106</v>
       </c>
       <c r="V3" t="n">
         <v>0.5642</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. VAZQUEZ JEREZ</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.581</v>
+        <v>1.0488</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2931</v>
+        <v>2.832</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7121</v>
+        <v>-1.7831</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7204</v>
+        <v>0.5557</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1582</v>
+        <v>-0.917</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5623</v>
+        <v>1.4726</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3113</v>
+        <v>2.2866</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5242</v>
+        <v>-0.276</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2129</v>
+        <v>2.5626</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0317</v>
+        <v>-1.731</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6824</v>
+        <v>-0.641</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6506</v>
+        <v>-1.09</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5523</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5821</v>
+        <v>-0.1486</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6684</v>
+        <v>0.2916</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9137</v>
+        <v>-0.4402</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2716</v>
+        <v>1.2239</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4477</v>
+        <v>1.2239</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VIDAL RODRIGUEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4768</v>
+        <v>0.5302</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4098</v>
+        <v>1.9988</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.933</v>
+        <v>-1.4686</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9558</v>
+        <v>1.1152</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3007</v>
+        <v>0.2043</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6551</v>
+        <v>0.9109</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2242</v>
+        <v>3.4374</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0618</v>
+        <v>2.0926</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1624</v>
+        <v>1.3447</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.18</v>
+        <v>-2.3221</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3625</v>
+        <v>-1.8883</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8175</v>
+        <v>-0.4338</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4908</v>
+        <v>0.521</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6797</v>
+        <v>0.0555</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1889</v>
+        <v>0.4655</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9418</v>
+        <v>-0.3299</v>
       </c>
       <c r="W5" t="n">
-        <v>1.506</v>
+        <v>-0.3299</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>A. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4516</v>
+        <v>-0.0143</v>
       </c>
       <c r="E6" t="n">
-        <v>2.371</v>
+        <v>2.1095</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9194</v>
+        <v>-2.1238</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5557</v>
+        <v>-0.9558</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.917</v>
+        <v>-0.3007</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4726</v>
+        <v>-0.6551</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2866</v>
+        <v>0.2242</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.276</v>
+        <v>0.0618</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5626</v>
+        <v>0.1624</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.731</v>
+        <v>-1.18</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.641</v>
+        <v>-0.3625</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.09</v>
+        <v>-0.8175</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7458</v>
+        <v>-0.0003</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1694</v>
+        <v>0.3794</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5765</v>
+        <v>-0.3796</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2239</v>
+        <v>0.9418</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>D. VAZQUEZ JEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2277</v>
+        <v>-0.2894</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0779</v>
+        <v>0.6135</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8502</v>
+        <v>-0.9029</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1152</v>
+        <v>-0.7204</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2043</v>
+        <v>-0.1582</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9109</v>
+        <v>-0.5623</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4374</v>
+        <v>0.3113</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0926</v>
+        <v>1.5242</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3447</v>
+        <v>-1.2129</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3221</v>
+        <v>-1.0317</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8883</v>
+        <v>-1.6824</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4338</v>
+        <v>0.6506</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7761</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2185</v>
+        <v>0.7117</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1346</v>
+        <v>-0.0112</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0839</v>
+        <v>0.7229</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3299</v>
+        <v>1.2716</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3299</v>
+        <v>2.4477</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6522</v>
+        <v>-0.3915</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8575</v>
+        <v>1.1183</v>
       </c>
       <c r="F8" t="n">
         <v>-1.5098</v>
@@ -1078,10 +1078,10 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.037</v>
+        <v>0.2238</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0359</v>
+        <v>0.2249</v>
       </c>
       <c r="U8" t="n">
         <v>-0.0011</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0752</v>
+        <v>-0.9601</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4211</v>
+        <v>-0.3606</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6541</v>
+        <v>-0.5996</v>
       </c>
       <c r="G9" t="n">
         <v>0.1132</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2183</v>
+        <v>-0.1032</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1211</v>
+        <v>-0.0606</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1823</v>
+        <v>-2.2941</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7019</v>
+        <v>2.263</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.8842</v>
+        <v>-4.5571</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9787</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1155</v>
+        <v>-0.2274</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3993</v>
+        <v>0.1618</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.3892</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2821</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7911</v>
+        <v>-6.2672</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.542</v>
+        <v>-2.8818</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2491</v>
+        <v>-3.3854</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0591</v>
@@ -1312,13 +1312,13 @@
         <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2068</v>
+        <v>0.7307</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0565</v>
+        <v>0.7167</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1503</v>
+        <v>0.014</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2821</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3909000000000002</v>
+        <v>0.5177000000000005</v>
       </c>
       <c r="E12" t="n">
-        <v>20.6876</v>
+        <v>21.5962</v>
       </c>
       <c r="F12" t="n">
         <v>-21.0784</v>
@@ -1357,7 +1357,7 @@
         <v>6.613700000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7826999999999995</v>
+        <v>-0.7827</v>
       </c>
       <c r="I12" t="n">
         <v>7.396199999999999</v>
@@ -1390,13 +1390,13 @@
         <v>3.8807</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7255</v>
+        <v>3.6341</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1607</v>
+        <v>2.0693</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5648</v>
+        <v>1.5649</v>
       </c>
       <c r="V12" t="n">
         <v>0.9417</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7557</v>
+        <v>4.6678</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5989</v>
+        <v>6.2987</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8433</v>
+        <v>-1.6308</v>
       </c>
       <c r="G13" t="n">
         <v>3.3732</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2183</v>
+        <v>0.1304</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4621</v>
+        <v>0.1618</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2438</v>
+        <v>-0.0314</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2529</v>
+        <v>4.0299</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7457</v>
+        <v>5.448</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4928</v>
+        <v>-1.4181</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2883</v>
+        <v>0.8053</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6197</v>
+        <v>1.665</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3314</v>
+        <v>-0.8597</v>
       </c>
       <c r="J14" t="n">
-        <v>5.7567</v>
+        <v>4.3108</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2296</v>
+        <v>2.451</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5271</v>
+        <v>1.8597</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.4683</v>
+        <v>-3.5054</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6099</v>
+        <v>-0.786</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.8585</v>
+        <v>-2.7195</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7463</v>
+        <v>2.1344</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7164</v>
+        <v>2.1344</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0056</v>
+        <v>-0.4635</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2647</v>
+        <v>-0.0867</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7409</v>
+        <v>-0.3768</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2239</v>
+        <v>1.5537</v>
       </c>
       <c r="W14" t="n">
         <v>1.2239</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2446</v>
+        <v>3.3741</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1477</v>
+        <v>5.5455</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.903</v>
+        <v>-2.1713</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8053</v>
+        <v>1.2883</v>
       </c>
       <c r="H15" t="n">
-        <v>1.665</v>
+        <v>1.6197</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8597</v>
+        <v>-0.3314</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3108</v>
+        <v>5.7567</v>
       </c>
       <c r="K15" t="n">
-        <v>2.451</v>
+        <v>3.2296</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8597</v>
+        <v>2.5271</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.5054</v>
+        <v>-4.4683</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.786</v>
+        <v>-1.6099</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.7195</v>
+        <v>-2.8585</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1344</v>
+        <v>1.7463</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1344</v>
+        <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2488</v>
+        <v>-0.8844</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.387</v>
+        <v>-0.4649</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8618</v>
+        <v>-0.4194</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5537</v>
+        <v>1.2239</v>
       </c>
       <c r="W15" t="n">
         <v>1.2239</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7472</v>
+        <v>1.3717</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1253</v>
+        <v>2.4256</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3782</v>
+        <v>-1.0539</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1501</v>
@@ -1702,13 +1702,13 @@
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0729</v>
+        <v>-0.4484</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6539</v>
+        <v>-0.3536</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.419</v>
+        <v>-0.0948</v>
       </c>
       <c r="V16" t="n">
         <v>1.2239</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.466</v>
+        <v>0.6206</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0412</v>
+        <v>0.1413</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4248</v>
+        <v>0.4793</v>
       </c>
       <c r="G17" t="n">
         <v>0.2356</v>
@@ -1780,13 +1780,13 @@
         <v>0.194</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0363</v>
+        <v>0.1909</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6492</v>
+        <v>-0.5462</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2037</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8528</v>
+        <v>-0.4496</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8503</v>
@@ -1858,13 +1858,13 @@
         <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2131</v>
+        <v>0.316</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4621</v>
+        <v>0.1618</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.249</v>
+        <v>0.1542</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5642</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9487</v>
+        <v>-1.4398</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7524</v>
+        <v>0.4521</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7011</v>
+        <v>-1.8918</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1192</v>
@@ -1936,13 +1936,13 @@
         <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2003</v>
+        <v>-0.2908</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2557</v>
+        <v>-0.0446</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0554</v>
+        <v>-0.2462</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>J. GALLETTO LAMELA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.081</v>
+        <v>-2.5833</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9947</v>
+        <v>-0.1863</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.0756</v>
+        <v>-2.3969</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9218</v>
+        <v>-0.0056</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7161</v>
+        <v>-0.6434</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2057</v>
+        <v>0.6379</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.08890000000000001</v>
+        <v>2.6099</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2513</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1624</v>
+        <v>1.8725</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8329</v>
+        <v>-2.6154</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4649</v>
+        <v>-1.3808</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3681</v>
+        <v>-1.2346</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9702</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2483</v>
+        <v>0.5462</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0134</v>
+        <v>-0.12</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2349</v>
+        <v>0.6662</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3776</v>
+        <v>-0.9896</v>
       </c>
       <c r="W20" t="n">
-        <v>2.0701</v>
+        <v>0.2343</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4477</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GALLETTO LAMELA</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0927</v>
+        <v>-2.6355</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5867</v>
+        <v>1.7945</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.506</v>
+        <v>-4.4299</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0056</v>
+        <v>-2.9218</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6434</v>
+        <v>-1.7161</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6379</v>
+        <v>-1.2057</v>
       </c>
       <c r="J21" t="n">
-        <v>2.6099</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7374000000000001</v>
+        <v>-0.2513</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8725</v>
+        <v>0.1624</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6154</v>
+        <v>-2.8329</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3808</v>
+        <v>-1.4649</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2346</v>
+        <v>-1.3681</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.1344</v>
+        <v>0.9702</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0368</v>
+        <v>-0.3062</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5204</v>
+        <v>-0.1868</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5572</v>
+        <v>-0.1194</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9896</v>
+        <v>-0.3776</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2343</v>
+        <v>2.0701</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.304</v>
+        <v>-5.1339</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9444</v>
+        <v>-0.7442</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3596</v>
+        <v>-4.3896</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2692</v>
@@ -2170,13 +2170,13 @@
         <v>2.3284</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3513</v>
+        <v>-0.1811</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9321</v>
+        <v>-0.7319</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5808</v>
+        <v>0.5507</v>
       </c>
       <c r="V22" t="n">
         <v>-3.0119</v>
@@ -2203,31 +2203,31 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3907999999999996</v>
+        <v>1.725400000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>21.0785</v>
+        <v>21.0786</v>
       </c>
       <c r="F23" t="n">
-        <v>-20.6876</v>
+        <v>-19.3526</v>
       </c>
       <c r="G23" t="n">
         <v>-6.613799999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7828000000000011</v>
+        <v>0.7827999999999995</v>
       </c>
       <c r="I23" t="n">
         <v>-7.3963</v>
       </c>
       <c r="J23" t="n">
-        <v>20.2657</v>
+        <v>20.26570000000001</v>
       </c>
       <c r="K23" t="n">
         <v>12.6465</v>
       </c>
       <c r="L23" t="n">
-        <v>7.619300000000001</v>
+        <v>7.619299999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-26.8792</v>
@@ -2248,13 +2248,13 @@
         <v>14.5525</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.7255</v>
+        <v>-1.3909</v>
       </c>
       <c r="T23" t="n">
         <v>-1.5648</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1607</v>
+        <v>0.1739</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9417999999999997</v>
